--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874918</v>
       </c>
       <c r="B2" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129874920</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874918</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129874920</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874918</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129874920</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874918</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129874920</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874918</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129874920</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129874918</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129874920</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>78852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129874918</v>
+        <v>129874920</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454062</v>
+        <v>454060</v>
       </c>
       <c r="R2" t="n">
-        <v>6894395</v>
+        <v>6894430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129874920</v>
+        <v>129874918</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454060</v>
+        <v>454062</v>
       </c>
       <c r="R3" t="n">
-        <v>6894430</v>
+        <v>6894395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29729-2024 artfynd.xlsx
+++ b/artfynd/A 29729-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874920</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>